--- a/app/samples/sample_report_rp053_full_template.xlsx
+++ b/app/samples/sample_report_rp053_full_template.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="271">
   <si>
-    <t>Результаты работы январь 2025</t>
+    <t>13.02.2024-25.06.2026</t>
   </si>
   <si>
     <t>Показатель</t>
@@ -52216,6 +52216,6 @@
     <mergeCell ref="Y3:Y4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>